--- a/artfynd/A 9526-2024 artfynd.xlsx
+++ b/artfynd/A 9526-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115310948</v>
+        <v>115310915</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>102975</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,14 +705,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -789,49 +784,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115311005</v>
+        <v>115311068</v>
       </c>
       <c r="B3" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -903,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115310915</v>
+        <v>115311005</v>
       </c>
       <c r="B4" t="n">
-        <v>57223</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,33 +904,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102975</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1020,12 +1005,7 @@
         <v>115310907</v>
       </c>
       <c r="B5" t="n">
-        <v>57412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,42 +1111,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115311068</v>
+        <v>115310948</v>
       </c>
       <c r="B6" t="n">
-        <v>57284</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>103042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>

--- a/artfynd/A 9526-2024 artfynd.xlsx
+++ b/artfynd/A 9526-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115310915</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115311068</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115311005</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115310907</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,8 +1242,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115310948</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>